--- a/Zzz_data/LMDO data_3i/vehicles_vietnam.xlsx
+++ b/Zzz_data/LMDO data_3i/vehicles_vietnam.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A UEH_UNIVERSITY\UEH_Subjects\LMDO\Lastmile\Zzz_data\LMDO data_3i\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F08E44-2E43-466A-8995-293840836ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1114,8 +1120,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1178,13 +1184,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1222,7 +1236,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1256,6 +1270,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1290,9 +1305,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1465,11 +1481,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J301"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1518,7 +1545,7 @@
         <v>11.7</v>
       </c>
       <c r="F2">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G2">
         <v>140</v>
@@ -1533,7 +1560,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1565,7 +1592,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1576,13 +1603,13 @@
         <v>1493</v>
       </c>
       <c r="D4">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E4">
         <v>65.03</v>
       </c>
       <c r="F4">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G4">
         <v>218</v>
@@ -1597,7 +1624,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1614,7 +1641,7 @@
         <v>60.92</v>
       </c>
       <c r="F5">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G5">
         <v>196</v>
@@ -1629,7 +1656,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1661,7 +1688,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1672,7 +1699,7 @@
         <v>896</v>
       </c>
       <c r="D7">
-        <v>9.210000000000001</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="E7">
         <v>71.48</v>
@@ -1693,7 +1720,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1710,7 +1737,7 @@
         <v>5.86</v>
       </c>
       <c r="F8">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G8">
         <v>45</v>
@@ -1725,7 +1752,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1742,7 +1769,7 @@
         <v>7.21</v>
       </c>
       <c r="F9">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G9">
         <v>36</v>
@@ -1757,7 +1784,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1789,7 +1816,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1821,7 +1848,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1838,7 +1865,7 @@
         <v>6.54</v>
       </c>
       <c r="F12">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G12">
         <v>28</v>
@@ -1853,7 +1880,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1885,7 +1912,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1917,7 +1944,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1931,7 +1958,7 @@
         <v>0.46</v>
       </c>
       <c r="E15">
-        <v>9.640000000000001</v>
+        <v>9.64</v>
       </c>
       <c r="F15">
         <v>0.11</v>
@@ -1949,7 +1976,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1981,7 +2008,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1995,7 +2022,7 @@
         <v>10.58</v>
       </c>
       <c r="E17">
-        <v>67.59999999999999</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="F17">
         <v>0.26</v>
@@ -2013,7 +2040,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2045,7 +2072,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2062,7 +2089,7 @@
         <v>5.29</v>
       </c>
       <c r="F19">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G19">
         <v>34</v>
@@ -2077,7 +2104,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2088,10 +2115,10 @@
         <v>88</v>
       </c>
       <c r="D20">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E20">
-        <v>9.890000000000001</v>
+        <v>9.89</v>
       </c>
       <c r="F20">
         <v>0.09</v>
@@ -2109,7 +2136,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2141,7 +2168,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2152,7 +2179,7 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E22">
         <v>7.38</v>
@@ -2173,7 +2200,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2205,7 +2232,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2222,7 +2249,7 @@
         <v>13.56</v>
       </c>
       <c r="F24">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G24">
         <v>99</v>
@@ -2237,7 +2264,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2269,7 +2296,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2301,7 +2328,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2312,7 +2339,7 @@
         <v>1067</v>
       </c>
       <c r="D27">
-        <v>8.619999999999999</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="E27">
         <v>61.03</v>
@@ -2333,7 +2360,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2350,7 +2377,7 @@
         <v>11.99</v>
       </c>
       <c r="F28">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G28">
         <v>108</v>
@@ -2365,7 +2392,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2397,7 +2424,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2429,7 +2456,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2461,7 +2488,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2493,7 +2520,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2507,7 +2534,7 @@
         <v>0.21</v>
       </c>
       <c r="E33">
-        <v>9.279999999999999</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="F33">
         <v>0.08</v>
@@ -2525,7 +2552,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2539,7 +2566,7 @@
         <v>0.11</v>
       </c>
       <c r="E34">
-        <v>9.710000000000001</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="F34">
         <v>0.08</v>
@@ -2557,7 +2584,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2589,7 +2616,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2621,7 +2648,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2632,7 +2659,7 @@
         <v>829</v>
       </c>
       <c r="D37">
-        <v>8.619999999999999</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="E37">
         <v>60.91</v>
@@ -2653,7 +2680,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2685,7 +2712,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2717,7 +2744,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2749,7 +2776,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2766,7 +2793,7 @@
         <v>57.2</v>
       </c>
       <c r="F41">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G41">
         <v>179</v>
@@ -2781,7 +2808,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2813,7 +2840,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2845,7 +2872,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2877,7 +2904,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2909,7 +2936,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -2941,7 +2968,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2973,7 +3000,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2987,7 +3014,7 @@
         <v>0.35</v>
       </c>
       <c r="E48">
-        <v>9.529999999999999</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="F48">
         <v>0.04</v>
@@ -3005,7 +3032,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -3022,7 +3049,7 @@
         <v>52.81</v>
       </c>
       <c r="F49">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G49">
         <v>326</v>
@@ -3037,7 +3064,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -3069,7 +3096,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -3101,7 +3128,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -3133,7 +3160,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -3147,7 +3174,7 @@
         <v>8.51</v>
       </c>
       <c r="E53">
-        <v>40.59</v>
+        <v>40.590000000000003</v>
       </c>
       <c r="F53">
         <v>0.16</v>
@@ -3165,7 +3192,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -3182,7 +3209,7 @@
         <v>53.97</v>
       </c>
       <c r="F54">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G54">
         <v>211</v>
@@ -3197,7 +3224,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -3211,7 +3238,7 @@
         <v>0.53</v>
       </c>
       <c r="E55">
-        <v>9.699999999999999</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F55">
         <v>0.09</v>
@@ -3229,7 +3256,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -3246,7 +3273,7 @@
         <v>9.49</v>
       </c>
       <c r="F56">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G56">
         <v>28</v>
@@ -3261,7 +3288,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -3293,7 +3320,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -3325,7 +3352,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -3336,7 +3363,7 @@
         <v>1242</v>
       </c>
       <c r="D59">
-        <v>10.05</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="E59">
         <v>55.84</v>
@@ -3357,7 +3384,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -3389,7 +3416,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -3421,7 +3448,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -3432,10 +3459,10 @@
         <v>1498</v>
       </c>
       <c r="D62">
-        <v>9.720000000000001</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="E62">
-        <v>72.06999999999999</v>
+        <v>72.069999999999993</v>
       </c>
       <c r="F62">
         <v>0.19</v>
@@ -3453,7 +3480,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -3485,7 +3512,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -3517,7 +3544,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -3528,7 +3555,7 @@
         <v>833</v>
       </c>
       <c r="D65">
-        <v>9.359999999999999</v>
+        <v>9.36</v>
       </c>
       <c r="E65">
         <v>50.14</v>
@@ -3549,7 +3576,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -3566,7 +3593,7 @@
         <v>61.87</v>
       </c>
       <c r="F66">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G66">
         <v>218</v>
@@ -3581,7 +3608,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -3613,7 +3640,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -3645,7 +3672,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -3677,7 +3704,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -3709,7 +3736,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -3741,7 +3768,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -3773,7 +3800,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -3787,7 +3814,7 @@
         <v>0.34</v>
       </c>
       <c r="E73">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="F73">
         <v>0.05</v>
@@ -3805,7 +3832,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -3837,7 +3864,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -3869,7 +3896,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -3901,7 +3928,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -3912,7 +3939,7 @@
         <v>1196</v>
       </c>
       <c r="D77">
-        <v>9.960000000000001</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="E77">
         <v>48.46</v>
@@ -3933,7 +3960,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>86</v>
       </c>
@@ -3965,7 +3992,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -3982,7 +4009,7 @@
         <v>11.29</v>
       </c>
       <c r="F79">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G79">
         <v>93</v>
@@ -3997,7 +4024,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -4029,7 +4056,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -4061,7 +4088,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -4093,7 +4120,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -4110,7 +4137,7 @@
         <v>63.41</v>
       </c>
       <c r="F83">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G83">
         <v>192</v>
@@ -4125,7 +4152,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -4157,7 +4184,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -4171,7 +4198,7 @@
         <v>10.53</v>
       </c>
       <c r="E85">
-        <v>73.70999999999999</v>
+        <v>73.709999999999994</v>
       </c>
       <c r="F85">
         <v>0.18</v>
@@ -4189,7 +4216,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -4221,7 +4248,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -4253,7 +4280,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>96</v>
       </c>
@@ -4285,7 +4312,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -4317,7 +4344,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -4349,7 +4376,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -4381,7 +4408,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>100</v>
       </c>
@@ -4413,7 +4440,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -4445,7 +4472,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>102</v>
       </c>
@@ -4477,7 +4504,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>103</v>
       </c>
@@ -4509,7 +4536,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -4520,7 +4547,7 @@
         <v>1048</v>
       </c>
       <c r="D96">
-        <v>8.359999999999999</v>
+        <v>8.36</v>
       </c>
       <c r="E96">
         <v>56.1</v>
@@ -4541,7 +4568,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -4573,7 +4600,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>106</v>
       </c>
@@ -4584,7 +4611,7 @@
         <v>1235</v>
       </c>
       <c r="D98">
-        <v>8.050000000000001</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="E98">
         <v>55.62</v>
@@ -4605,7 +4632,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -4637,7 +4664,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -4648,13 +4675,13 @@
         <v>81</v>
       </c>
       <c r="D100">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E100">
         <v>14.38</v>
       </c>
       <c r="F100">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G100">
         <v>115</v>
@@ -4669,7 +4696,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>109</v>
       </c>
@@ -4686,7 +4713,7 @@
         <v>14.47</v>
       </c>
       <c r="F101">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G101">
         <v>96</v>
@@ -4701,7 +4728,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>110</v>
       </c>
@@ -4733,7 +4760,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>111</v>
       </c>
@@ -4765,7 +4792,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>112</v>
       </c>
@@ -4797,7 +4824,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>113</v>
       </c>
@@ -4829,7 +4856,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -4840,7 +4867,7 @@
         <v>50</v>
       </c>
       <c r="D106">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E106">
         <v>11.44</v>
@@ -4861,7 +4888,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>115</v>
       </c>
@@ -4893,7 +4920,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>116</v>
       </c>
@@ -4907,7 +4934,7 @@
         <v>8.92</v>
       </c>
       <c r="E108">
-        <v>67.06999999999999</v>
+        <v>67.069999999999993</v>
       </c>
       <c r="F108">
         <v>0.13</v>
@@ -4925,7 +4952,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>117</v>
       </c>
@@ -4957,7 +4984,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>118</v>
       </c>
@@ -4989,7 +5016,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>119</v>
       </c>
@@ -5021,7 +5048,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -5053,7 +5080,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>121</v>
       </c>
@@ -5085,7 +5112,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>122</v>
       </c>
@@ -5117,7 +5144,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>123</v>
       </c>
@@ -5149,7 +5176,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>124</v>
       </c>
@@ -5181,7 +5208,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>125</v>
       </c>
@@ -5192,7 +5219,7 @@
         <v>57</v>
       </c>
       <c r="D117">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E117">
         <v>8.26</v>
@@ -5213,7 +5240,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>126</v>
       </c>
@@ -5245,7 +5272,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>127</v>
       </c>
@@ -5277,7 +5304,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>128</v>
       </c>
@@ -5309,7 +5336,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>129</v>
       </c>
@@ -5326,7 +5353,7 @@
         <v>13.27</v>
       </c>
       <c r="F121">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G121">
         <v>94</v>
@@ -5341,7 +5368,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>130</v>
       </c>
@@ -5373,7 +5400,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -5405,7 +5432,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -5437,7 +5464,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -5469,7 +5496,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>134</v>
       </c>
@@ -5501,7 +5528,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>135</v>
       </c>
@@ -5515,7 +5542,7 @@
         <v>0.68</v>
       </c>
       <c r="E127">
-        <v>9.380000000000001</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="F127">
         <v>0.11</v>
@@ -5533,7 +5560,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>136</v>
       </c>
@@ -5550,7 +5577,7 @@
         <v>65.25</v>
       </c>
       <c r="F128">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G128">
         <v>201</v>
@@ -5565,7 +5592,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>137</v>
       </c>
@@ -5597,7 +5624,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>138</v>
       </c>
@@ -5611,7 +5638,7 @@
         <v>6.49</v>
       </c>
       <c r="E130">
-        <v>40.09</v>
+        <v>40.090000000000003</v>
       </c>
       <c r="F130">
         <v>0.16</v>
@@ -5629,7 +5656,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -5661,7 +5688,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>140</v>
       </c>
@@ -5678,7 +5705,7 @@
         <v>49.31</v>
       </c>
       <c r="F132">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G132">
         <v>207</v>
@@ -5693,7 +5720,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>141</v>
       </c>
@@ -5725,7 +5752,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>142</v>
       </c>
@@ -5757,7 +5784,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>143</v>
       </c>
@@ -5789,7 +5816,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>144</v>
       </c>
@@ -5803,7 +5830,7 @@
         <v>0.18</v>
       </c>
       <c r="E136">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="F136">
         <v>0.06</v>
@@ -5821,7 +5848,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>145</v>
       </c>
@@ -5853,7 +5880,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>146</v>
       </c>
@@ -5885,7 +5912,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>147</v>
       </c>
@@ -5917,7 +5944,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>148</v>
       </c>
@@ -5949,7 +5976,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>149</v>
       </c>
@@ -5981,7 +6008,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>150</v>
       </c>
@@ -6013,7 +6040,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>151</v>
       </c>
@@ -6045,7 +6072,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>152</v>
       </c>
@@ -6077,7 +6104,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>153</v>
       </c>
@@ -6109,7 +6136,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>154</v>
       </c>
@@ -6141,7 +6168,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>155</v>
       </c>
@@ -6152,7 +6179,7 @@
         <v>1095</v>
       </c>
       <c r="D147">
-        <v>9.970000000000001</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="E147">
         <v>54.98</v>
@@ -6173,7 +6200,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>156</v>
       </c>
@@ -6205,7 +6232,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>157</v>
       </c>
@@ -6237,7 +6264,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>158</v>
       </c>
@@ -6269,7 +6296,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>159</v>
       </c>
@@ -6301,7 +6328,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>160</v>
       </c>
@@ -6333,7 +6360,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>161</v>
       </c>
@@ -6365,7 +6392,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>162</v>
       </c>
@@ -6379,7 +6406,7 @@
         <v>0.23</v>
       </c>
       <c r="E154">
-        <v>9.039999999999999</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="F154">
         <v>0.04</v>
@@ -6397,7 +6424,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>163</v>
       </c>
@@ -6411,7 +6438,7 @@
         <v>0.12</v>
       </c>
       <c r="E155">
-        <v>8.960000000000001</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="F155">
         <v>0.05</v>
@@ -6429,7 +6456,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>164</v>
       </c>
@@ -6461,7 +6488,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>165</v>
       </c>
@@ -6493,7 +6520,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>166</v>
       </c>
@@ -6525,7 +6552,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>167</v>
       </c>
@@ -6557,7 +6584,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>168</v>
       </c>
@@ -6574,7 +6601,7 @@
         <v>6.21</v>
       </c>
       <c r="F160">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G160">
         <v>39</v>
@@ -6589,7 +6616,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>169</v>
       </c>
@@ -6621,7 +6648,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>170</v>
       </c>
@@ -6653,7 +6680,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>171</v>
       </c>
@@ -6685,7 +6712,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>172</v>
       </c>
@@ -6717,7 +6744,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>173</v>
       </c>
@@ -6749,7 +6776,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>174</v>
       </c>
@@ -6760,7 +6787,7 @@
         <v>79</v>
       </c>
       <c r="D166">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E166">
         <v>13.69</v>
@@ -6781,7 +6808,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>175</v>
       </c>
@@ -6813,7 +6840,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>176</v>
       </c>
@@ -6845,7 +6872,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>177</v>
       </c>
@@ -6877,7 +6904,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>178</v>
       </c>
@@ -6894,7 +6921,7 @@
         <v>78.86</v>
       </c>
       <c r="F170">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G170">
         <v>254</v>
@@ -6909,7 +6936,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>179</v>
       </c>
@@ -6941,7 +6968,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>180</v>
       </c>
@@ -6973,7 +7000,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>181</v>
       </c>
@@ -6984,7 +7011,7 @@
         <v>99</v>
       </c>
       <c r="D173">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E173">
         <v>10.23</v>
@@ -7005,7 +7032,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>182</v>
       </c>
@@ -7037,7 +7064,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>183</v>
       </c>
@@ -7069,7 +7096,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>184</v>
       </c>
@@ -7101,7 +7128,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>185</v>
       </c>
@@ -7133,7 +7160,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>186</v>
       </c>
@@ -7165,7 +7192,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>187</v>
       </c>
@@ -7197,7 +7224,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>188</v>
       </c>
@@ -7208,7 +7235,7 @@
         <v>85</v>
       </c>
       <c r="D180">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E180">
         <v>10.75</v>
@@ -7229,7 +7256,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>189</v>
       </c>
@@ -7261,7 +7288,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>190</v>
       </c>
@@ -7293,7 +7320,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>191</v>
       </c>
@@ -7307,7 +7334,7 @@
         <v>0.32</v>
       </c>
       <c r="E183">
-        <v>8.210000000000001</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F183">
         <v>0.04</v>
@@ -7325,7 +7352,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>192</v>
       </c>
@@ -7339,7 +7366,7 @@
         <v>8.06</v>
       </c>
       <c r="E184">
-        <v>75.59999999999999</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="F184">
         <v>0.23</v>
@@ -7357,7 +7384,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>193</v>
       </c>
@@ -7374,7 +7401,7 @@
         <v>6.37</v>
       </c>
       <c r="F185">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G185">
         <v>43</v>
@@ -7389,7 +7416,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>194</v>
       </c>
@@ -7421,7 +7448,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>195</v>
       </c>
@@ -7453,7 +7480,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>196</v>
       </c>
@@ -7485,7 +7512,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>197</v>
       </c>
@@ -7496,13 +7523,13 @@
         <v>52</v>
       </c>
       <c r="D189">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E189">
         <v>14.49</v>
       </c>
       <c r="F189">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G189">
         <v>109</v>
@@ -7517,7 +7544,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>198</v>
       </c>
@@ -7531,7 +7558,7 @@
         <v>0.38</v>
       </c>
       <c r="E190">
-        <v>9.369999999999999</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="F190">
         <v>0.1</v>
@@ -7549,7 +7576,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -7566,7 +7593,7 @@
         <v>14.23</v>
       </c>
       <c r="F191">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G191">
         <v>128</v>
@@ -7581,7 +7608,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>200</v>
       </c>
@@ -7613,7 +7640,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>201</v>
       </c>
@@ -7624,7 +7651,7 @@
         <v>98</v>
       </c>
       <c r="D193">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E193">
         <v>11.61</v>
@@ -7645,7 +7672,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>202</v>
       </c>
@@ -7656,13 +7683,13 @@
         <v>1137</v>
       </c>
       <c r="D194">
-        <v>8.289999999999999</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="E194">
         <v>43.09</v>
       </c>
       <c r="F194">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G194">
         <v>219</v>
@@ -7677,7 +7704,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>203</v>
       </c>
@@ -7694,7 +7721,7 @@
         <v>45.46</v>
       </c>
       <c r="F195">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G195">
         <v>222</v>
@@ -7709,7 +7736,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>204</v>
       </c>
@@ -7720,7 +7747,7 @@
         <v>37</v>
       </c>
       <c r="D196">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E196">
         <v>9.43</v>
@@ -7741,7 +7768,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>205</v>
       </c>
@@ -7773,7 +7800,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>206</v>
       </c>
@@ -7805,7 +7832,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>207</v>
       </c>
@@ -7837,7 +7864,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>208</v>
       </c>
@@ -7869,7 +7896,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>209</v>
       </c>
@@ -7880,7 +7907,7 @@
         <v>51</v>
       </c>
       <c r="D201">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="E201">
         <v>13.71</v>
@@ -7901,7 +7928,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>210</v>
       </c>
@@ -7912,10 +7939,10 @@
         <v>67</v>
       </c>
       <c r="D202">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="E202">
-        <v>8.130000000000001</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="F202">
         <v>0.09</v>
@@ -7933,7 +7960,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>211</v>
       </c>
@@ -7944,7 +7971,7 @@
         <v>80</v>
       </c>
       <c r="D203">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E203">
         <v>13.77</v>
@@ -7965,7 +7992,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>212</v>
       </c>
@@ -7997,7 +8024,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>213</v>
       </c>
@@ -8029,7 +8056,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>214</v>
       </c>
@@ -8061,7 +8088,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>215</v>
       </c>
@@ -8093,7 +8120,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>216</v>
       </c>
@@ -8110,7 +8137,7 @@
         <v>10.18</v>
       </c>
       <c r="F208">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G208">
         <v>141</v>
@@ -8125,7 +8152,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>217</v>
       </c>
@@ -8139,7 +8166,7 @@
         <v>0.37</v>
       </c>
       <c r="E209">
-        <v>8.880000000000001</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="F209">
         <v>0.04</v>
@@ -8157,7 +8184,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>218</v>
       </c>
@@ -8189,7 +8216,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>219</v>
       </c>
@@ -8206,7 +8233,7 @@
         <v>9.85</v>
       </c>
       <c r="F211">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G211">
         <v>27</v>
@@ -8221,7 +8248,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>220</v>
       </c>
@@ -8253,7 +8280,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>221</v>
       </c>
@@ -8285,7 +8312,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>222</v>
       </c>
@@ -8299,10 +8326,10 @@
         <v>6.96</v>
       </c>
       <c r="E214">
-        <v>65.90000000000001</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="F214">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G214">
         <v>129</v>
@@ -8317,7 +8344,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>223</v>
       </c>
@@ -8331,7 +8358,7 @@
         <v>0.76</v>
       </c>
       <c r="E215">
-        <v>9.279999999999999</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="F215">
         <v>0.08</v>
@@ -8349,7 +8376,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>224</v>
       </c>
@@ -8381,7 +8408,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>225</v>
       </c>
@@ -8413,7 +8440,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>226</v>
       </c>
@@ -8445,7 +8472,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>227</v>
       </c>
@@ -8477,7 +8504,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>228</v>
       </c>
@@ -8509,7 +8536,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>229</v>
       </c>
@@ -8523,7 +8550,7 @@
         <v>0.45</v>
       </c>
       <c r="E221">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="F221">
         <v>0.06</v>
@@ -8541,7 +8568,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>230</v>
       </c>
@@ -8573,7 +8600,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>231</v>
       </c>
@@ -8590,7 +8617,7 @@
         <v>5.28</v>
       </c>
       <c r="F223">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G223">
         <v>48</v>
@@ -8605,7 +8632,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>232</v>
       </c>
@@ -8619,7 +8646,7 @@
         <v>0.41</v>
       </c>
       <c r="E224">
-        <v>9.109999999999999</v>
+        <v>9.11</v>
       </c>
       <c r="F224">
         <v>0.05</v>
@@ -8637,7 +8664,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>233</v>
       </c>
@@ -8669,7 +8696,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>234</v>
       </c>
@@ -8701,7 +8728,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>235</v>
       </c>
@@ -8715,7 +8742,7 @@
         <v>0.23</v>
       </c>
       <c r="E227">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="F227">
         <v>0.09</v>
@@ -8733,7 +8760,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>236</v>
       </c>
@@ -8744,7 +8771,7 @@
         <v>1296</v>
       </c>
       <c r="D228">
-        <v>9.210000000000001</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="E228">
         <v>77.19</v>
@@ -8765,7 +8792,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>237</v>
       </c>
@@ -8776,7 +8803,7 @@
         <v>129</v>
       </c>
       <c r="D229">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E229">
         <v>17.18</v>
@@ -8797,7 +8824,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>238</v>
       </c>
@@ -8811,7 +8838,7 @@
         <v>0.31</v>
       </c>
       <c r="E230">
-        <v>8.640000000000001</v>
+        <v>8.64</v>
       </c>
       <c r="F230">
         <v>0.04</v>
@@ -8829,7 +8856,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>239</v>
       </c>
@@ -8861,7 +8888,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>240</v>
       </c>
@@ -8893,7 +8920,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>241</v>
       </c>
@@ -8907,7 +8934,7 @@
         <v>10.27</v>
       </c>
       <c r="E233">
-        <v>65.15000000000001</v>
+        <v>65.150000000000006</v>
       </c>
       <c r="F233">
         <v>0.12</v>
@@ -8925,7 +8952,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>242</v>
       </c>
@@ -8936,13 +8963,13 @@
         <v>84</v>
       </c>
       <c r="D234">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E234">
         <v>10.43</v>
       </c>
       <c r="F234">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G234">
         <v>137</v>
@@ -8957,7 +8984,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>243</v>
       </c>
@@ -8968,7 +8995,7 @@
         <v>77</v>
       </c>
       <c r="D235">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E235">
         <v>14.7</v>
@@ -8989,7 +9016,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>244</v>
       </c>
@@ -9021,7 +9048,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>245</v>
       </c>
@@ -9053,7 +9080,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>246</v>
       </c>
@@ -9085,7 +9112,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>247</v>
       </c>
@@ -9096,7 +9123,7 @@
         <v>128</v>
       </c>
       <c r="D239">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="E239">
         <v>17.12</v>
@@ -9117,7 +9144,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>248</v>
       </c>
@@ -9149,7 +9176,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>249</v>
       </c>
@@ -9181,7 +9208,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>250</v>
       </c>
@@ -9195,7 +9222,7 @@
         <v>8.85</v>
       </c>
       <c r="E242">
-        <v>67.31999999999999</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="F242">
         <v>0.18</v>
@@ -9213,7 +9240,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>251</v>
       </c>
@@ -9245,7 +9272,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>252</v>
       </c>
@@ -9277,7 +9304,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>253</v>
       </c>
@@ -9309,7 +9336,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>254</v>
       </c>
@@ -9341,7 +9368,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>255</v>
       </c>
@@ -9373,7 +9400,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>256</v>
       </c>
@@ -9405,7 +9432,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>257</v>
       </c>
@@ -9416,7 +9443,7 @@
         <v>98</v>
       </c>
       <c r="D249">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E249">
         <v>12.13</v>
@@ -9437,7 +9464,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>258</v>
       </c>
@@ -9469,7 +9496,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>259</v>
       </c>
@@ -9501,7 +9528,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>260</v>
       </c>
@@ -9512,7 +9539,7 @@
         <v>40</v>
       </c>
       <c r="D252">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E252">
         <v>9.25</v>
@@ -9533,7 +9560,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>261</v>
       </c>
@@ -9565,7 +9592,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>262</v>
       </c>
@@ -9579,7 +9606,7 @@
         <v>7.07</v>
       </c>
       <c r="E254">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="F254">
         <v>0.11</v>
@@ -9597,7 +9624,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>263</v>
       </c>
@@ -9614,7 +9641,7 @@
         <v>48.91</v>
       </c>
       <c r="F255">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G255">
         <v>285</v>
@@ -9629,7 +9656,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>264</v>
       </c>
@@ -9661,7 +9688,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>265</v>
       </c>
@@ -9672,13 +9699,13 @@
         <v>40</v>
       </c>
       <c r="D257">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E257">
         <v>9.23</v>
       </c>
       <c r="F257">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G257">
         <v>49</v>
@@ -9693,7 +9720,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>266</v>
       </c>
@@ -9725,7 +9752,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>267</v>
       </c>
@@ -9736,7 +9763,7 @@
         <v>887</v>
       </c>
       <c r="D259">
-        <v>8.609999999999999</v>
+        <v>8.61</v>
       </c>
       <c r="E259">
         <v>46.69</v>
@@ -9757,7 +9784,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>268</v>
       </c>
@@ -9789,7 +9816,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>269</v>
       </c>
@@ -9821,7 +9848,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>270</v>
       </c>
@@ -9832,7 +9859,7 @@
         <v>57</v>
       </c>
       <c r="D262">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="E262">
         <v>10.63</v>
@@ -9853,7 +9880,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>271</v>
       </c>
@@ -9885,7 +9912,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>272</v>
       </c>
@@ -9917,7 +9944,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>273</v>
       </c>
@@ -9949,7 +9976,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>274</v>
       </c>
@@ -9981,7 +10008,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>275</v>
       </c>
@@ -9998,7 +10025,7 @@
         <v>75.03</v>
       </c>
       <c r="F267">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G267">
         <v>316</v>
@@ -10013,7 +10040,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>276</v>
       </c>
@@ -10045,7 +10072,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>277</v>
       </c>
@@ -10056,7 +10083,7 @@
         <v>1170</v>
       </c>
       <c r="D269">
-        <v>8.369999999999999</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="E269">
         <v>56.53</v>
@@ -10077,7 +10104,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>278</v>
       </c>
@@ -10109,7 +10136,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>279</v>
       </c>
@@ -10141,7 +10168,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>280</v>
       </c>
@@ -10173,7 +10200,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>281</v>
       </c>
@@ -10205,7 +10232,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>282</v>
       </c>
@@ -10237,7 +10264,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>283</v>
       </c>
@@ -10269,7 +10296,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>284</v>
       </c>
@@ -10301,7 +10328,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>285</v>
       </c>
@@ -10312,7 +10339,7 @@
         <v>959</v>
       </c>
       <c r="D277">
-        <v>8.859999999999999</v>
+        <v>8.86</v>
       </c>
       <c r="E277">
         <v>62.8</v>
@@ -10333,7 +10360,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>286</v>
       </c>
@@ -10365,7 +10392,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>287</v>
       </c>
@@ -10376,7 +10403,7 @@
         <v>76</v>
       </c>
       <c r="D279">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="E279">
         <v>12.53</v>
@@ -10397,7 +10424,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>288</v>
       </c>
@@ -10429,7 +10456,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>289</v>
       </c>
@@ -10443,10 +10470,10 @@
         <v>0.22</v>
       </c>
       <c r="E281">
-        <v>9.869999999999999</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="F281">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G281">
         <v>25</v>
@@ -10461,7 +10488,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>290</v>
       </c>
@@ -10493,7 +10520,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>291</v>
       </c>
@@ -10504,7 +10531,7 @@
         <v>58</v>
       </c>
       <c r="D283">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="E283">
         <v>14.33</v>
@@ -10525,7 +10552,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>292</v>
       </c>
@@ -10542,7 +10569,7 @@
         <v>12.69</v>
       </c>
       <c r="F284">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G284">
         <v>73</v>
@@ -10557,7 +10584,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>293</v>
       </c>
@@ -10589,7 +10616,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>294</v>
       </c>
@@ -10621,7 +10648,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>295</v>
       </c>
@@ -10638,7 +10665,7 @@
         <v>53.02</v>
       </c>
       <c r="F287">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G287">
         <v>253</v>
@@ -10653,7 +10680,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>296</v>
       </c>
@@ -10670,7 +10697,7 @@
         <v>45.37</v>
       </c>
       <c r="F288">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G288">
         <v>135</v>
@@ -10685,7 +10712,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>297</v>
       </c>
@@ -10717,7 +10744,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>298</v>
       </c>
@@ -10728,7 +10755,7 @@
         <v>1391</v>
       </c>
       <c r="D290">
-        <v>8.609999999999999</v>
+        <v>8.61</v>
       </c>
       <c r="E290">
         <v>74.55</v>
@@ -10749,7 +10776,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>299</v>
       </c>
@@ -10781,7 +10808,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>300</v>
       </c>
@@ -10795,7 +10822,7 @@
         <v>0.26</v>
       </c>
       <c r="E292">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="F292">
         <v>0.09</v>
@@ -10813,7 +10840,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>301</v>
       </c>
@@ -10845,7 +10872,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>302</v>
       </c>
@@ -10877,7 +10904,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>303</v>
       </c>
@@ -10909,7 +10936,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>304</v>
       </c>
@@ -10920,7 +10947,7 @@
         <v>929</v>
       </c>
       <c r="D296">
-        <v>9.039999999999999</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="E296">
         <v>57.86</v>
@@ -10941,7 +10968,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>305</v>
       </c>
@@ -10973,7 +11000,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>306</v>
       </c>
@@ -10987,7 +11014,7 @@
         <v>0.12</v>
       </c>
       <c r="E298">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F298">
         <v>0.05</v>
@@ -11005,7 +11032,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>307</v>
       </c>
@@ -11037,7 +11064,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>308</v>
       </c>
@@ -11054,7 +11081,7 @@
         <v>10.32</v>
       </c>
       <c r="F300">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G300">
         <v>156</v>
@@ -11069,7 +11096,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>309</v>
       </c>
